--- a/05 - FicherosInforme/01InformeVentas/01InformeVentas.xlsx
+++ b/05 - FicherosInforme/01InformeVentas/01InformeVentas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\PowerBI\05 - FicherosInforme\01InformeVentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6821B32-8A47-4ABD-8826-2A864D182F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2029781E-0C95-49FD-B67E-0DC8A33DC470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="388">
   <si>
     <t>ClienteID</t>
   </si>
@@ -45,606 +45,6 @@
     <t>País</t>
   </si>
   <si>
-    <t>Mark Norris</t>
-  </si>
-  <si>
-    <t>michael88@example.net</t>
-  </si>
-  <si>
-    <t>Matthew Berg</t>
-  </si>
-  <si>
-    <t>benjaminhayes@example.net</t>
-  </si>
-  <si>
-    <t>Cody Daniels</t>
-  </si>
-  <si>
-    <t>christopherking@example.net</t>
-  </si>
-  <si>
-    <t>Phillip Foster</t>
-  </si>
-  <si>
-    <t>djohnson@example.net</t>
-  </si>
-  <si>
-    <t>Kara Pacheco</t>
-  </si>
-  <si>
-    <t>feliciahernandez@example.org</t>
-  </si>
-  <si>
-    <t>Dalton Flores</t>
-  </si>
-  <si>
-    <t>linda21@example.net</t>
-  </si>
-  <si>
-    <t>John Graves</t>
-  </si>
-  <si>
-    <t>yfrederick@example.com</t>
-  </si>
-  <si>
-    <t>Janice Williams</t>
-  </si>
-  <si>
-    <t>yriley@example.org</t>
-  </si>
-  <si>
-    <t>Daniel Smith</t>
-  </si>
-  <si>
-    <t>jacob29@example.net</t>
-  </si>
-  <si>
-    <t>Debra Wiley</t>
-  </si>
-  <si>
-    <t>larry05@example.org</t>
-  </si>
-  <si>
-    <t>Julie Gonzalez</t>
-  </si>
-  <si>
-    <t>mathewsjason@example.org</t>
-  </si>
-  <si>
-    <t>Brianna Richardson</t>
-  </si>
-  <si>
-    <t>lauraperez@example.org</t>
-  </si>
-  <si>
-    <t>William Cox</t>
-  </si>
-  <si>
-    <t>perkinsdarren@example.com</t>
-  </si>
-  <si>
-    <t>Sarah Franco</t>
-  </si>
-  <si>
-    <t>jasmineknight@example.org</t>
-  </si>
-  <si>
-    <t>Connor Contreras</t>
-  </si>
-  <si>
-    <t>bbowman@example.org</t>
-  </si>
-  <si>
-    <t>Michelle Berry</t>
-  </si>
-  <si>
-    <t>simpsonbobby@example.com</t>
-  </si>
-  <si>
-    <t>Stephen Boyle</t>
-  </si>
-  <si>
-    <t>marissamorrow@example.net</t>
-  </si>
-  <si>
-    <t>Samantha Valdez</t>
-  </si>
-  <si>
-    <t>molly57@example.com</t>
-  </si>
-  <si>
-    <t>Kaitlin Schneider</t>
-  </si>
-  <si>
-    <t>vgarcia@example.com</t>
-  </si>
-  <si>
-    <t>Allison Payne</t>
-  </si>
-  <si>
-    <t>olivia19@example.org</t>
-  </si>
-  <si>
-    <t>Brianna Wallace</t>
-  </si>
-  <si>
-    <t>ncharles@example.org</t>
-  </si>
-  <si>
-    <t>Matthew Smith</t>
-  </si>
-  <si>
-    <t>ortizamanda@example.net</t>
-  </si>
-  <si>
-    <t>Carol Robbins</t>
-  </si>
-  <si>
-    <t>robert50@example.com</t>
-  </si>
-  <si>
-    <t>Jesse Edwards</t>
-  </si>
-  <si>
-    <t>matthew22@example.net</t>
-  </si>
-  <si>
-    <t>Kristopher Miller</t>
-  </si>
-  <si>
-    <t>uthomas@example.org</t>
-  </si>
-  <si>
-    <t>Joe Lee</t>
-  </si>
-  <si>
-    <t>snydertravis@example.com</t>
-  </si>
-  <si>
-    <t>Steven Bass</t>
-  </si>
-  <si>
-    <t>georgesalinas@example.com</t>
-  </si>
-  <si>
-    <t>Mr. Henry Shea</t>
-  </si>
-  <si>
-    <t>kellermichael@example.com</t>
-  </si>
-  <si>
-    <t>Julie Walker</t>
-  </si>
-  <si>
-    <t>nlong@example.org</t>
-  </si>
-  <si>
-    <t>Tanya Prince</t>
-  </si>
-  <si>
-    <t>samantha13@example.org</t>
-  </si>
-  <si>
-    <t>Phillip Aguilar</t>
-  </si>
-  <si>
-    <t>michael51@example.com</t>
-  </si>
-  <si>
-    <t>Chloe Hudson</t>
-  </si>
-  <si>
-    <t>castillokelly@example.org</t>
-  </si>
-  <si>
-    <t>Jason Reese</t>
-  </si>
-  <si>
-    <t>hannah31@example.org</t>
-  </si>
-  <si>
-    <t>Devin Ramos</t>
-  </si>
-  <si>
-    <t>danielperry@example.net</t>
-  </si>
-  <si>
-    <t>Sarah Hunter</t>
-  </si>
-  <si>
-    <t>debra08@example.org</t>
-  </si>
-  <si>
-    <t>Trevor Thomas</t>
-  </si>
-  <si>
-    <t>aprilmoyer@example.org</t>
-  </si>
-  <si>
-    <t>Sarah Holt</t>
-  </si>
-  <si>
-    <t>davidcampbell@example.net</t>
-  </si>
-  <si>
-    <t>George Pena</t>
-  </si>
-  <si>
-    <t>bruce93@example.org</t>
-  </si>
-  <si>
-    <t>Denise Schmidt</t>
-  </si>
-  <si>
-    <t>dominiqueallen@example.org</t>
-  </si>
-  <si>
-    <t>Jeanette Anderson</t>
-  </si>
-  <si>
-    <t>kelsey42@example.com</t>
-  </si>
-  <si>
-    <t>Christopher Parker</t>
-  </si>
-  <si>
-    <t>sanchezbrandon@example.net</t>
-  </si>
-  <si>
-    <t>Jason Wright</t>
-  </si>
-  <si>
-    <t>stephen82@example.org</t>
-  </si>
-  <si>
-    <t>Anthony Ramos</t>
-  </si>
-  <si>
-    <t>alison81@example.org</t>
-  </si>
-  <si>
-    <t>Dustin Walker</t>
-  </si>
-  <si>
-    <t>narroyo@example.com</t>
-  </si>
-  <si>
-    <t>Joseph Rivera</t>
-  </si>
-  <si>
-    <t>chaselogan@example.net</t>
-  </si>
-  <si>
-    <t>David Reilly</t>
-  </si>
-  <si>
-    <t>steven99@example.net</t>
-  </si>
-  <si>
-    <t>Kelly Knapp</t>
-  </si>
-  <si>
-    <t>johnbutler@example.com</t>
-  </si>
-  <si>
-    <t>Madison Mendoza</t>
-  </si>
-  <si>
-    <t>sarahcampbell@example.org</t>
-  </si>
-  <si>
-    <t>Charlene Ingram</t>
-  </si>
-  <si>
-    <t>jlopez@example.com</t>
-  </si>
-  <si>
-    <t>Michael Lawrence</t>
-  </si>
-  <si>
-    <t>madisonroberts@example.net</t>
-  </si>
-  <si>
-    <t>Joseph Powell</t>
-  </si>
-  <si>
-    <t>samanthacox@example.net</t>
-  </si>
-  <si>
-    <t>James Cherry</t>
-  </si>
-  <si>
-    <t>schultzcharles@example.net</t>
-  </si>
-  <si>
-    <t>Joshua Shannon</t>
-  </si>
-  <si>
-    <t>nfrazier@example.com</t>
-  </si>
-  <si>
-    <t>Sara Griffith</t>
-  </si>
-  <si>
-    <t>alyssataylor@example.com</t>
-  </si>
-  <si>
-    <t>Cathy Porter</t>
-  </si>
-  <si>
-    <t>griffindiana@example.org</t>
-  </si>
-  <si>
-    <t>Debra Rice</t>
-  </si>
-  <si>
-    <t>colecassandra@example.org</t>
-  </si>
-  <si>
-    <t>Erin Meyer</t>
-  </si>
-  <si>
-    <t>javierfuller@example.com</t>
-  </si>
-  <si>
-    <t>David Hickman</t>
-  </si>
-  <si>
-    <t>juliebenton@example.com</t>
-  </si>
-  <si>
-    <t>Shannon Duran</t>
-  </si>
-  <si>
-    <t>torresrobert@example.net</t>
-  </si>
-  <si>
-    <t>Adam Colon</t>
-  </si>
-  <si>
-    <t>kellyruiz@example.net</t>
-  </si>
-  <si>
-    <t>David Simpson</t>
-  </si>
-  <si>
-    <t>williamwilliams@example.net</t>
-  </si>
-  <si>
-    <t>Cole Krueger</t>
-  </si>
-  <si>
-    <t>cramirez@example.net</t>
-  </si>
-  <si>
-    <t>Brian Hopkins</t>
-  </si>
-  <si>
-    <t>jessicarice@example.com</t>
-  </si>
-  <si>
-    <t>Beverly Frazier</t>
-  </si>
-  <si>
-    <t>jennifertorres@example.net</t>
-  </si>
-  <si>
-    <t>Anna Melton</t>
-  </si>
-  <si>
-    <t>alutz@example.com</t>
-  </si>
-  <si>
-    <t>Stephanie King</t>
-  </si>
-  <si>
-    <t>pharris@example.org</t>
-  </si>
-  <si>
-    <t>Brandon Lynn</t>
-  </si>
-  <si>
-    <t>fletcherjasmine@example.org</t>
-  </si>
-  <si>
-    <t>Kyle Fleming</t>
-  </si>
-  <si>
-    <t>roberthernandez@example.net</t>
-  </si>
-  <si>
-    <t>Mr. Mike Reeves</t>
-  </si>
-  <si>
-    <t>bpetersen@example.net</t>
-  </si>
-  <si>
-    <t>Leah Little</t>
-  </si>
-  <si>
-    <t>stuartbrian@example.org</t>
-  </si>
-  <si>
-    <t>Brian Navarro</t>
-  </si>
-  <si>
-    <t>kturner@example.net</t>
-  </si>
-  <si>
-    <t>Michael Buckley</t>
-  </si>
-  <si>
-    <t>denisestevens@example.com</t>
-  </si>
-  <si>
-    <t>Dr. Anthony Crawford</t>
-  </si>
-  <si>
-    <t>jmcdonald@example.org</t>
-  </si>
-  <si>
-    <t>Ashley Moss</t>
-  </si>
-  <si>
-    <t>jeffjones@example.org</t>
-  </si>
-  <si>
-    <t>Ray Davis</t>
-  </si>
-  <si>
-    <t>fthomas@example.net</t>
-  </si>
-  <si>
-    <t>Lucas Adams</t>
-  </si>
-  <si>
-    <t>lkeller@example.net</t>
-  </si>
-  <si>
-    <t>Dana Fisher</t>
-  </si>
-  <si>
-    <t>kimberlybrown@example.org</t>
-  </si>
-  <si>
-    <t>Corey Roy</t>
-  </si>
-  <si>
-    <t>janicelee@example.net</t>
-  </si>
-  <si>
-    <t>Kevin Johnson</t>
-  </si>
-  <si>
-    <t>lmeyers@example.org</t>
-  </si>
-  <si>
-    <t>Kerry Frye</t>
-  </si>
-  <si>
-    <t>gilberttyler@example.com</t>
-  </si>
-  <si>
-    <t>Jennifer Johnson</t>
-  </si>
-  <si>
-    <t>rnash@example.com</t>
-  </si>
-  <si>
-    <t>Lisa Maxwell</t>
-  </si>
-  <si>
-    <t>ann38@example.net</t>
-  </si>
-  <si>
-    <t>Theresa Snow</t>
-  </si>
-  <si>
-    <t>wdavis@example.net</t>
-  </si>
-  <si>
-    <t>Jeffery Mason</t>
-  </si>
-  <si>
-    <t>catherinemunoz@example.com</t>
-  </si>
-  <si>
-    <t>Charles Ford</t>
-  </si>
-  <si>
-    <t>kimberlycox@example.net</t>
-  </si>
-  <si>
-    <t>Mr. Michael Vargas</t>
-  </si>
-  <si>
-    <t>hawkinsbrianna@example.net</t>
-  </si>
-  <si>
-    <t>George Spencer</t>
-  </si>
-  <si>
-    <t>bakertravis@example.net</t>
-  </si>
-  <si>
-    <t>Manuel Boyd</t>
-  </si>
-  <si>
-    <t>lawrencejennifer@example.org</t>
-  </si>
-  <si>
-    <t>Thomas Wiggins</t>
-  </si>
-  <si>
-    <t>rachelwise@example.net</t>
-  </si>
-  <si>
-    <t>David Martinez</t>
-  </si>
-  <si>
-    <t>vbaldwin@example.com</t>
-  </si>
-  <si>
-    <t>Jose Dougherty</t>
-  </si>
-  <si>
-    <t>samantha62@example.org</t>
-  </si>
-  <si>
-    <t>Justin Castro</t>
-  </si>
-  <si>
-    <t>robert01@example.org</t>
-  </si>
-  <si>
-    <t>Diane Webb</t>
-  </si>
-  <si>
-    <t>anthony52@example.org</t>
-  </si>
-  <si>
-    <t>Melinda Salas</t>
-  </si>
-  <si>
-    <t>qray@example.org</t>
-  </si>
-  <si>
-    <t>James Powell</t>
-  </si>
-  <si>
-    <t>karen32@example.net</t>
-  </si>
-  <si>
-    <t>Julie Burns</t>
-  </si>
-  <si>
-    <t>kathryn23@example.net</t>
-  </si>
-  <si>
-    <t>Lisa Williams DDS</t>
-  </si>
-  <si>
-    <t>lhanson@example.com</t>
-  </si>
-  <si>
-    <t>Sylvia Cross</t>
-  </si>
-  <si>
-    <t>johnsimon@example.net</t>
-  </si>
-  <si>
-    <t>Kimberly Griffin</t>
-  </si>
-  <si>
-    <t>tracymiller@example.com</t>
-  </si>
-  <si>
-    <t>Hunter Hopkins</t>
-  </si>
-  <si>
-    <t>kristen57@example.org</t>
-  </si>
-  <si>
     <t>CategoriaID</t>
   </si>
   <si>
@@ -660,9 +60,6 @@
     <t>Hogar</t>
   </si>
   <si>
-    <t>Juguetes</t>
-  </si>
-  <si>
     <t>ProductoID</t>
   </si>
   <si>
@@ -672,150 +69,6 @@
     <t>PrecioUnitario</t>
   </si>
   <si>
-    <t>Meet</t>
-  </si>
-  <si>
-    <t>Voice</t>
-  </si>
-  <si>
-    <t>Lose</t>
-  </si>
-  <si>
-    <t>Fish</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Marriage</t>
-  </si>
-  <si>
-    <t>Maybe</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Whatever</t>
-  </si>
-  <si>
-    <t>Process</t>
-  </si>
-  <si>
-    <t>Stand</t>
-  </si>
-  <si>
-    <t>Ago</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Party</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Establish</t>
-  </si>
-  <si>
-    <t>Keep</t>
-  </si>
-  <si>
-    <t>Staff</t>
-  </si>
-  <si>
-    <t>Democrat</t>
-  </si>
-  <si>
-    <t>Finally</t>
-  </si>
-  <si>
-    <t>Little</t>
-  </si>
-  <si>
-    <t>Couple</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>Might</t>
-  </si>
-  <si>
-    <t>Focus</t>
-  </si>
-  <si>
-    <t>Magazine</t>
-  </si>
-  <si>
-    <t>Political</t>
-  </si>
-  <si>
-    <t>Much</t>
-  </si>
-  <si>
-    <t>Congress</t>
-  </si>
-  <si>
-    <t>Visit</t>
-  </si>
-  <si>
-    <t>Song</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>Hot</t>
-  </si>
-  <si>
-    <t>Institution</t>
-  </si>
-  <si>
-    <t>Look</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Perform</t>
-  </si>
-  <si>
-    <t>Raise</t>
-  </si>
-  <si>
-    <t>Challenge</t>
-  </si>
-  <si>
-    <t>Describe</t>
-  </si>
-  <si>
-    <t>Also</t>
-  </si>
-  <si>
-    <t>Cell</t>
-  </si>
-  <si>
-    <t>Threat</t>
-  </si>
-  <si>
     <t>EmpleadoID</t>
   </si>
   <si>
@@ -1294,6 +547,648 @@
   </si>
   <si>
     <t>787705050</t>
+  </si>
+  <si>
+    <t>Marta Sánchez</t>
+  </si>
+  <si>
+    <t>Carlos Jiménez</t>
+  </si>
+  <si>
+    <t>Francisco Jiménez</t>
+  </si>
+  <si>
+    <t>Carmen Álvarez</t>
+  </si>
+  <si>
+    <t>María López</t>
+  </si>
+  <si>
+    <t>Carmen Díaz</t>
+  </si>
+  <si>
+    <t>Ana López</t>
+  </si>
+  <si>
+    <t>Javier Gómez</t>
+  </si>
+  <si>
+    <t>javier.gomez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Sara Gutiérrez</t>
+  </si>
+  <si>
+    <t>sara.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Laura García</t>
+  </si>
+  <si>
+    <t>laura.garcia@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Isabel Romero</t>
+  </si>
+  <si>
+    <t>isabel.romero@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carmen Muñoz</t>
+  </si>
+  <si>
+    <t>carmen.munoz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Isabel López</t>
+  </si>
+  <si>
+    <t>isabel.lopez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Patricia Martínez</t>
+  </si>
+  <si>
+    <t>patricia.martinez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>José Domínguez</t>
+  </si>
+  <si>
+    <t>jose.dominguez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>ana.lopez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carlos Muñoz</t>
+  </si>
+  <si>
+    <t>carlos.munoz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Francisco Torres</t>
+  </si>
+  <si>
+    <t>francisco.torres@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Luis Domínguez</t>
+  </si>
+  <si>
+    <t>luis.dominguez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>María Navarro</t>
+  </si>
+  <si>
+    <t>maria.navarro@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Lucía Navarro</t>
+  </si>
+  <si>
+    <t>lucia.navarro@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Lucía Pérez</t>
+  </si>
+  <si>
+    <t>lucia.perez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Elena Álvarez</t>
+  </si>
+  <si>
+    <t>elena.alvarez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Ana Ruiz</t>
+  </si>
+  <si>
+    <t>ana.ruiz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Lucía Moreno</t>
+  </si>
+  <si>
+    <t>lucia.moreno@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Elena Navarro</t>
+  </si>
+  <si>
+    <t>elena.navarro@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Jesús Romero</t>
+  </si>
+  <si>
+    <t>jesus.romero@ejemplo.com</t>
+  </si>
+  <si>
+    <t>David Torres</t>
+  </si>
+  <si>
+    <t>david.torres@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Isabel Álvarez</t>
+  </si>
+  <si>
+    <t>isabel.alvarez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>francisco.jimenez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Manuel Romero</t>
+  </si>
+  <si>
+    <t>manuel.romero@ejemplo.com</t>
+  </si>
+  <si>
+    <t>marta.sanchez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>José Moreno</t>
+  </si>
+  <si>
+    <t>jose.moreno@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Manuel Martín</t>
+  </si>
+  <si>
+    <t>manuel.martin@ejemplo.com</t>
+  </si>
+  <si>
+    <t>María Gómez</t>
+  </si>
+  <si>
+    <t>maria.gomez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Sara Pérez</t>
+  </si>
+  <si>
+    <t>sara.perez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carmen Pérez</t>
+  </si>
+  <si>
+    <t>carmen.perez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Luis Gutiérrez</t>
+  </si>
+  <si>
+    <t>luis.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>carmen.alvarez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Patricia Muñoz</t>
+  </si>
+  <si>
+    <t>patricia.munoz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Elena Gutiérrez</t>
+  </si>
+  <si>
+    <t>elena.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Isabel Hernández</t>
+  </si>
+  <si>
+    <t>isabel.hernandez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Manuel Domínguez</t>
+  </si>
+  <si>
+    <t>manuel.dominguez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Antonio Gutiérrez</t>
+  </si>
+  <si>
+    <t>antonio.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Ana Romero</t>
+  </si>
+  <si>
+    <t>ana.romero@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Elena Moreno</t>
+  </si>
+  <si>
+    <t>elena.moreno@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Manuel Torres</t>
+  </si>
+  <si>
+    <t>manuel.torres@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Javier Martínez</t>
+  </si>
+  <si>
+    <t>javier.martinez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Manuel Muñoz</t>
+  </si>
+  <si>
+    <t>manuel.munoz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carmen Martín</t>
+  </si>
+  <si>
+    <t>carmen.martin@ejemplo.com</t>
+  </si>
+  <si>
+    <t>David Martín</t>
+  </si>
+  <si>
+    <t>david.martin@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Jesús Hernández</t>
+  </si>
+  <si>
+    <t>jesus.hernandez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Javier Pérez</t>
+  </si>
+  <si>
+    <t>javier.perez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Marta Torres</t>
+  </si>
+  <si>
+    <t>marta.torres@ejemplo.com</t>
+  </si>
+  <si>
+    <t>María García</t>
+  </si>
+  <si>
+    <t>maria.garcia@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Marta Martín</t>
+  </si>
+  <si>
+    <t>marta.martin@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Jesús Álvarez</t>
+  </si>
+  <si>
+    <t>jesus.alvarez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Javier Moreno</t>
+  </si>
+  <si>
+    <t>javier.moreno@ejemplo.com</t>
+  </si>
+  <si>
+    <t>maria.lopez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Manuel López</t>
+  </si>
+  <si>
+    <t>manuel.lopez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carlos Hernández</t>
+  </si>
+  <si>
+    <t>carlos.hernandez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Ana Gutiérrez</t>
+  </si>
+  <si>
+    <t>ana.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Jesús Ruiz</t>
+  </si>
+  <si>
+    <t>jesus.ruiz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Lucía Domínguez</t>
+  </si>
+  <si>
+    <t>lucia.dominguez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>David Gutiérrez</t>
+  </si>
+  <si>
+    <t>david.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carlos López</t>
+  </si>
+  <si>
+    <t>carlos.lopez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>David Hernández</t>
+  </si>
+  <si>
+    <t>david.hernandez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Laura Jiménez</t>
+  </si>
+  <si>
+    <t>laura.jimenez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Jesús López</t>
+  </si>
+  <si>
+    <t>jesus.lopez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Javier Hernández</t>
+  </si>
+  <si>
+    <t>javier.hernandez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carmen Ruiz</t>
+  </si>
+  <si>
+    <t>carmen.ruiz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Luis Álvarez</t>
+  </si>
+  <si>
+    <t>luis.alvarez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Elena Domínguez</t>
+  </si>
+  <si>
+    <t>elena.dominguez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Francisco Martínez</t>
+  </si>
+  <si>
+    <t>francisco.martinez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>David Sánchez</t>
+  </si>
+  <si>
+    <t>david.sanchez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Patricia Torres</t>
+  </si>
+  <si>
+    <t>patricia.torres@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Isabel Gómez</t>
+  </si>
+  <si>
+    <t>isabel.gomez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carmen Gómez</t>
+  </si>
+  <si>
+    <t>carmen.gomez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>carmen.diaz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>María Gutiérrez</t>
+  </si>
+  <si>
+    <t>maria.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Carmen López</t>
+  </si>
+  <si>
+    <t>carmen.lopez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>José Alonso</t>
+  </si>
+  <si>
+    <t>jose.alonso@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Javier Torres</t>
+  </si>
+  <si>
+    <t>javier.torres@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Francisco García</t>
+  </si>
+  <si>
+    <t>francisco.garcia@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Elena Muñoz</t>
+  </si>
+  <si>
+    <t>elena.munoz@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Jesús García</t>
+  </si>
+  <si>
+    <t>jesus.garcia@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Isabel Sánchez</t>
+  </si>
+  <si>
+    <t>isabel.sanchez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Marta Gutiérrez</t>
+  </si>
+  <si>
+    <t>marta.gutierrez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>carlos.jimenez@ejemplo.com</t>
+  </si>
+  <si>
+    <t>Ocio</t>
+  </si>
+  <si>
+    <t>Juguetes Serie 761</t>
+  </si>
+  <si>
+    <t>Electrónica Serie 374</t>
+  </si>
+  <si>
+    <t>Libros Serie 870</t>
+  </si>
+  <si>
+    <t>Electrónica Serie 606</t>
+  </si>
+  <si>
+    <t>Hogar Modelo 777</t>
+  </si>
+  <si>
+    <t>Juguetes Serie 276</t>
+  </si>
+  <si>
+    <t>Juguetes Tipo 854</t>
+  </si>
+  <si>
+    <t>Juguetes Serie 511</t>
+  </si>
+  <si>
+    <t>Electrónica Tipo 992</t>
+  </si>
+  <si>
+    <t>Ropa Modelo 638</t>
+  </si>
+  <si>
+    <t>Juguetes Modelo 649</t>
+  </si>
+  <si>
+    <t>Alimentos Serie 814</t>
+  </si>
+  <si>
+    <t>Juguetes Serie 781</t>
+  </si>
+  <si>
+    <t>Alimentos Tipo 157</t>
+  </si>
+  <si>
+    <t>Hogar Modelo 680</t>
+  </si>
+  <si>
+    <t>Hogar Modelo 938</t>
+  </si>
+  <si>
+    <t>Alimentos Modelo 456</t>
+  </si>
+  <si>
+    <t>Electrónica Serie 152</t>
+  </si>
+  <si>
+    <t>Ropa Modelo 290</t>
+  </si>
+  <si>
+    <t>Alimentos Serie 294</t>
+  </si>
+  <si>
+    <t>Libros Serie 150</t>
+  </si>
+  <si>
+    <t>Ropa Serie 523</t>
+  </si>
+  <si>
+    <t>Electrónica Modelo 286</t>
+  </si>
+  <si>
+    <t>Electrónica Serie 525</t>
+  </si>
+  <si>
+    <t>Alimentos Serie 629</t>
+  </si>
+  <si>
+    <t>Libros Tipo 138</t>
+  </si>
+  <si>
+    <t>Ropa Serie 502</t>
+  </si>
+  <si>
+    <t>Electrónica Serie 109</t>
+  </si>
+  <si>
+    <t>Ropa Tipo 664</t>
+  </si>
+  <si>
+    <t>Alimentos Serie 146</t>
+  </si>
+  <si>
+    <t>Ropa Tipo 216</t>
+  </si>
+  <si>
+    <t>Juguetes Serie 338</t>
+  </si>
+  <si>
+    <t>Ropa Modelo 872</t>
+  </si>
+  <si>
+    <t>Libros Tipo 808</t>
+  </si>
+  <si>
+    <t>Libros Modelo 485</t>
+  </si>
+  <si>
+    <t>Libros Modelo 258</t>
+  </si>
+  <si>
+    <t>Libros Modelo 328</t>
+  </si>
+  <si>
+    <t>Juguetes Modelo 596</t>
+  </si>
+  <si>
+    <t>Libros Modelo 573</t>
+  </si>
+  <si>
+    <t>Hogar Serie 236</t>
+  </si>
+  <si>
+    <t>Juguetes Tipo 164</t>
+  </si>
+  <si>
+    <t>Libros Tipo 752</t>
+  </si>
+  <si>
+    <t>Hogar Tipo 579</t>
+  </si>
+  <si>
+    <t>Ropa Tipo 204</t>
+  </si>
+  <si>
+    <t>Electrónica Tipo 716</t>
+  </si>
+  <si>
+    <t>Hogar Tipo 836</t>
+  </si>
+  <si>
+    <t>Juguetes Tipo 487</t>
+  </si>
+  <si>
+    <t>Alimentos Modelo 244</t>
+  </si>
+  <si>
+    <t>Ropa Modelo 357</t>
   </si>
 </sst>
 </file>
@@ -1353,12 +1248,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1695,2000 +1591,2000 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
+      <c r="B2" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>294</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>295</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>296</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+      <c r="B3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>298</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+      <c r="B4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>301</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="B5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
+      <c r="B6" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
+      <c r="B7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="D7" t="s">
-        <v>306</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
+      <c r="B8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>301</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
+      <c r="B9" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="D9" t="s">
-        <v>309</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
+      <c r="B10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="D10" t="s">
-        <v>311</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
+      <c r="B11" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="D11" t="s">
-        <v>313</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>298</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
+      <c r="B12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>314</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>301</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
+      <c r="B13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>315</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
+      <c r="B14" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="D14" t="s">
-        <v>316</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
+      <c r="B15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="D15" t="s">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>319</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>35</v>
+      <c r="B16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>320</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>321</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
+      <c r="B17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="D17" t="s">
-        <v>322</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>323</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
+      <c r="B18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="D18" t="s">
-        <v>324</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>312</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
+      <c r="B19" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D19" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>319</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>43</v>
+      <c r="B20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="D20" t="s">
-        <v>326</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
+      <c r="B21" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="D21" t="s">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
         <v>47</v>
-      </c>
-      <c r="D22" t="s">
-        <v>330</v>
-      </c>
-      <c r="E22" t="s">
-        <v>331</v>
-      </c>
-      <c r="F22" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
+      <c r="B23" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="D23" t="s">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
         <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" t="s">
-        <v>334</v>
-      </c>
-      <c r="E24" t="s">
-        <v>317</v>
-      </c>
-      <c r="F24" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
+      <c r="B25" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="D25" t="s">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" t="s">
-        <v>55</v>
+      <c r="B26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>224</v>
       </c>
       <c r="D26" t="s">
-        <v>336</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" t="s">
-        <v>57</v>
+      <c r="B27" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="D27" t="s">
-        <v>337</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>338</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" t="s">
         <v>58</v>
       </c>
-      <c r="C28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" t="s">
-        <v>339</v>
-      </c>
-      <c r="E28" t="s">
-        <v>307</v>
-      </c>
       <c r="F28" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B29" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" t="s">
         <v>61</v>
       </c>
-      <c r="D29" t="s">
-        <v>340</v>
-      </c>
-      <c r="E29" t="s">
-        <v>310</v>
-      </c>
       <c r="F29" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" t="s">
-        <v>63</v>
+      <c r="B30" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="D30" t="s">
-        <v>341</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="F30" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" t="s">
-        <v>65</v>
+      <c r="B31" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>231</v>
       </c>
       <c r="D31" t="s">
-        <v>342</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>343</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" t="s">
-        <v>67</v>
+      <c r="B32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="D32" t="s">
-        <v>344</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>345</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" t="s">
-        <v>69</v>
+      <c r="B33" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="D33" t="s">
-        <v>346</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s">
-        <v>347</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" t="s">
-        <v>71</v>
+      <c r="B34" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="D34" t="s">
-        <v>348</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>349</v>
+        <v>100</v>
       </c>
       <c r="F34" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" t="s">
-        <v>73</v>
+      <c r="B35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="D35" t="s">
-        <v>350</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="F35" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>75</v>
+      <c r="B36" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>237</v>
       </c>
       <c r="D36" t="s">
-        <v>351</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="F36" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" t="s">
-        <v>77</v>
+      <c r="B37" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="D37" t="s">
-        <v>352</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
-        <v>343</v>
+        <v>94</v>
       </c>
       <c r="F37" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" t="s">
-        <v>79</v>
+      <c r="B38" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>239</v>
       </c>
       <c r="D38" t="s">
-        <v>353</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="F38" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>81</v>
+      <c r="B39" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="D39" t="s">
-        <v>355</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="F39" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
+      <c r="B40" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="D40" t="s">
-        <v>356</v>
+        <v>107</v>
       </c>
       <c r="E40" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="F40" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" t="s">
-        <v>85</v>
+      <c r="B41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D41" t="s">
-        <v>357</v>
+        <v>108</v>
       </c>
       <c r="E41" t="s">
-        <v>343</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" t="s">
-        <v>87</v>
+      <c r="B42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="D42" t="s">
-        <v>358</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="F42" t="s">
-        <v>296</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>89</v>
+      <c r="B43" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>248</v>
       </c>
       <c r="D43" t="s">
-        <v>359</v>
+        <v>110</v>
       </c>
       <c r="E43" t="s">
-        <v>301</v>
+        <v>52</v>
       </c>
       <c r="F43" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" t="s">
-        <v>91</v>
+      <c r="B44" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>250</v>
       </c>
       <c r="D44" t="s">
-        <v>360</v>
+        <v>111</v>
       </c>
       <c r="E44" t="s">
-        <v>361</v>
+        <v>112</v>
       </c>
       <c r="F44" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" t="s">
-        <v>93</v>
+      <c r="B45" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="D45" t="s">
-        <v>362</v>
+        <v>113</v>
       </c>
       <c r="E45" t="s">
-        <v>361</v>
+        <v>112</v>
       </c>
       <c r="F45" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" t="s">
-        <v>95</v>
+      <c r="B46" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="D46" t="s">
-        <v>363</v>
+        <v>114</v>
       </c>
       <c r="E46" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="F46" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" t="s">
-        <v>97</v>
+      <c r="B47" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>256</v>
       </c>
       <c r="D47" t="s">
-        <v>364</v>
+        <v>115</v>
       </c>
       <c r="E47" t="s">
-        <v>365</v>
+        <v>116</v>
       </c>
       <c r="F47" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" t="s">
-        <v>99</v>
+      <c r="B48" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>258</v>
       </c>
       <c r="D48" t="s">
-        <v>366</v>
+        <v>117</v>
       </c>
       <c r="E48" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="F48" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" t="s">
-        <v>101</v>
+      <c r="B49" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="D49" t="s">
-        <v>367</v>
+        <v>118</v>
       </c>
       <c r="E49" t="s">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" t="s">
-        <v>103</v>
+      <c r="B50" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>262</v>
       </c>
       <c r="D50" t="s">
-        <v>368</v>
+        <v>119</v>
       </c>
       <c r="E50" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="F50" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
-        <v>104</v>
-      </c>
-      <c r="C51" t="s">
-        <v>105</v>
+      <c r="B51" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="D51" t="s">
-        <v>369</v>
+        <v>120</v>
       </c>
       <c r="E51" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="F51" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" t="s">
-        <v>107</v>
+      <c r="B52" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>370</v>
+        <v>121</v>
       </c>
       <c r="E52" t="s">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="F52" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53" t="s">
-        <v>109</v>
+      <c r="B53" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="D53" t="s">
-        <v>371</v>
+        <v>122</v>
       </c>
       <c r="E53" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="F53" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" t="s">
-        <v>111</v>
+      <c r="B54" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>270</v>
       </c>
       <c r="D54" t="s">
-        <v>372</v>
+        <v>123</v>
       </c>
       <c r="E54" t="s">
-        <v>321</v>
+        <v>72</v>
       </c>
       <c r="F54" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
+      <c r="B55" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="D55" t="s">
-        <v>373</v>
+        <v>124</v>
       </c>
       <c r="E55" t="s">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="F55" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" t="s">
-        <v>115</v>
+      <c r="B56" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>272</v>
       </c>
       <c r="D56" t="s">
-        <v>374</v>
+        <v>125</v>
       </c>
       <c r="E56" t="s">
-        <v>321</v>
+        <v>72</v>
       </c>
       <c r="F56" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" t="s">
-        <v>117</v>
+      <c r="B57" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="D57" t="s">
-        <v>375</v>
+        <v>126</v>
       </c>
       <c r="E57" t="s">
-        <v>319</v>
+        <v>70</v>
       </c>
       <c r="F57" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>118</v>
-      </c>
-      <c r="C58" t="s">
-        <v>119</v>
+      <c r="B58" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="D58" t="s">
-        <v>376</v>
+        <v>127</v>
       </c>
       <c r="E58" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="F58" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>120</v>
-      </c>
-      <c r="C59" t="s">
-        <v>121</v>
+      <c r="B59" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="D59" t="s">
-        <v>377</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="F59" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>122</v>
-      </c>
-      <c r="C60" t="s">
-        <v>123</v>
+      <c r="B60" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="D60" t="s">
-        <v>378</v>
+        <v>129</v>
       </c>
       <c r="E60" t="s">
-        <v>349</v>
+        <v>100</v>
       </c>
       <c r="F60" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" t="s">
-        <v>125</v>
+      <c r="B61" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>281</v>
       </c>
       <c r="D61" t="s">
-        <v>379</v>
+        <v>130</v>
       </c>
       <c r="E61" t="s">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="F61" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" t="s">
-        <v>127</v>
+      <c r="B62" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="D62" t="s">
-        <v>380</v>
+        <v>131</v>
       </c>
       <c r="E62" t="s">
-        <v>381</v>
+        <v>132</v>
       </c>
       <c r="F62" t="s">
-        <v>296</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
-        <v>128</v>
-      </c>
-      <c r="C63" t="s">
-        <v>129</v>
+      <c r="B63" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="D63" t="s">
-        <v>382</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="F63" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
-        <v>130</v>
-      </c>
-      <c r="C64" t="s">
-        <v>131</v>
+      <c r="B64" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>287</v>
       </c>
       <c r="D64" t="s">
-        <v>383</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="F64" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
-        <v>132</v>
-      </c>
-      <c r="C65" t="s">
-        <v>133</v>
+      <c r="B65" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="D65" t="s">
-        <v>384</v>
+        <v>135</v>
       </c>
       <c r="E65" t="s">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="F65" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
-        <v>134</v>
-      </c>
-      <c r="C66" t="s">
-        <v>135</v>
+      <c r="B66" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="D66" t="s">
-        <v>385</v>
+        <v>136</v>
       </c>
       <c r="E66" t="s">
-        <v>361</v>
+        <v>112</v>
       </c>
       <c r="F66" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="B67" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D67" t="s">
         <v>137</v>
       </c>
-      <c r="D67" t="s">
-        <v>386</v>
-      </c>
       <c r="E67" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="F67" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D68" t="s">
         <v>138</v>
       </c>
-      <c r="C68" t="s">
-        <v>139</v>
-      </c>
-      <c r="D68" t="s">
-        <v>387</v>
-      </c>
       <c r="E68" t="s">
-        <v>305</v>
+        <v>56</v>
       </c>
       <c r="F68" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
-        <v>140</v>
-      </c>
-      <c r="C69" t="s">
-        <v>141</v>
+      <c r="B69" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="D69" t="s">
-        <v>388</v>
+        <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>303</v>
+        <v>54</v>
       </c>
       <c r="F69" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
-        <v>142</v>
-      </c>
-      <c r="C70" t="s">
-        <v>143</v>
+      <c r="B70" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="D70" t="s">
-        <v>389</v>
+        <v>140</v>
       </c>
       <c r="E70" t="s">
-        <v>361</v>
+        <v>112</v>
       </c>
       <c r="F70" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
-        <v>144</v>
-      </c>
-      <c r="C71" t="s">
-        <v>145</v>
+      <c r="B71" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="D71" t="s">
-        <v>390</v>
+        <v>141</v>
       </c>
       <c r="E71" t="s">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="F71" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" t="s">
-        <v>147</v>
+      <c r="B72" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="D72" t="s">
-        <v>391</v>
+        <v>142</v>
       </c>
       <c r="E72" t="s">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="F72" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
-        <v>148</v>
-      </c>
-      <c r="C73" t="s">
-        <v>149</v>
+      <c r="B73" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>303</v>
       </c>
       <c r="D73" t="s">
-        <v>392</v>
+        <v>143</v>
       </c>
       <c r="E73" t="s">
-        <v>301</v>
+        <v>52</v>
       </c>
       <c r="F73" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>150</v>
-      </c>
-      <c r="C74" t="s">
-        <v>151</v>
+      <c r="B74" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="D74" t="s">
-        <v>393</v>
+        <v>144</v>
       </c>
       <c r="E74" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="F74" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
-        <v>152</v>
-      </c>
-      <c r="C75" t="s">
-        <v>153</v>
+      <c r="B75" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="D75" t="s">
-        <v>394</v>
+        <v>145</v>
       </c>
       <c r="E75" t="s">
-        <v>298</v>
+        <v>49</v>
       </c>
       <c r="F75" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
-        <v>154</v>
-      </c>
-      <c r="C76" t="s">
-        <v>155</v>
+      <c r="B76" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="D76" t="s">
-        <v>395</v>
+        <v>146</v>
       </c>
       <c r="E76" t="s">
-        <v>312</v>
+        <v>63</v>
       </c>
       <c r="F76" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
-        <v>156</v>
-      </c>
-      <c r="C77" t="s">
-        <v>157</v>
+      <c r="B77" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="D77" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
       <c r="E77" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="F77" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
-        <v>158</v>
-      </c>
-      <c r="C78" t="s">
-        <v>159</v>
+      <c r="B78" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="D78" t="s">
-        <v>398</v>
+        <v>149</v>
       </c>
       <c r="E78" t="s">
-        <v>343</v>
+        <v>94</v>
       </c>
       <c r="F78" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
-        <v>160</v>
-      </c>
-      <c r="C79" t="s">
-        <v>161</v>
+      <c r="B79" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="D79" t="s">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="E79" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="F79" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
-        <v>162</v>
-      </c>
-      <c r="C80" t="s">
-        <v>163</v>
+      <c r="B80" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="D80" t="s">
-        <v>400</v>
+        <v>151</v>
       </c>
       <c r="E80" t="s">
-        <v>298</v>
+        <v>49</v>
       </c>
       <c r="F80" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
-        <v>164</v>
-      </c>
-      <c r="C81" t="s">
-        <v>165</v>
+      <c r="B81" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="D81" t="s">
-        <v>401</v>
+        <v>152</v>
       </c>
       <c r="E81" t="s">
-        <v>321</v>
+        <v>72</v>
       </c>
       <c r="F81" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
-        <v>166</v>
-      </c>
-      <c r="C82" t="s">
-        <v>167</v>
+      <c r="B82" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="D82" t="s">
-        <v>402</v>
+        <v>153</v>
       </c>
       <c r="E82" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="F82" t="s">
-        <v>296</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" t="s">
-        <v>169</v>
+      <c r="B83" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>317</v>
       </c>
       <c r="D83" t="s">
-        <v>403</v>
+        <v>154</v>
       </c>
       <c r="E83" t="s">
-        <v>338</v>
+        <v>89</v>
       </c>
       <c r="F83" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
-        <v>170</v>
-      </c>
-      <c r="C84" t="s">
-        <v>171</v>
+      <c r="B84" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="D84" t="s">
-        <v>404</v>
+        <v>155</v>
       </c>
       <c r="E84" t="s">
-        <v>319</v>
+        <v>70</v>
       </c>
       <c r="F84" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
-        <v>172</v>
-      </c>
-      <c r="C85" t="s">
-        <v>173</v>
+      <c r="B85" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="D85" t="s">
-        <v>405</v>
+        <v>156</v>
       </c>
       <c r="E85" t="s">
-        <v>338</v>
+        <v>89</v>
       </c>
       <c r="F85" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
-        <v>174</v>
-      </c>
-      <c r="C86" t="s">
-        <v>175</v>
+      <c r="B86" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="D86" t="s">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="E86" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="F86" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
-        <v>176</v>
-      </c>
-      <c r="C87" t="s">
-        <v>177</v>
+      <c r="B87" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="D87" t="s">
-        <v>407</v>
+        <v>158</v>
       </c>
       <c r="E87" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="F87" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
-        <v>178</v>
-      </c>
-      <c r="C88" t="s">
-        <v>179</v>
+      <c r="B88" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="D88" t="s">
-        <v>408</v>
+        <v>159</v>
       </c>
       <c r="E88" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="F88" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
-        <v>180</v>
-      </c>
-      <c r="C89" t="s">
-        <v>181</v>
+      <c r="B89" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="D89" t="s">
-        <v>409</v>
+        <v>160</v>
       </c>
       <c r="E89" t="s">
-        <v>347</v>
+        <v>98</v>
       </c>
       <c r="F89" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
-        <v>182</v>
-      </c>
-      <c r="C90" t="s">
-        <v>183</v>
+      <c r="B90" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="D90" t="s">
-        <v>410</v>
+        <v>161</v>
       </c>
       <c r="E90" t="s">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="F90" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
-        <v>184</v>
-      </c>
-      <c r="C91" t="s">
-        <v>185</v>
+      <c r="B91" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="D91" t="s">
-        <v>411</v>
+        <v>162</v>
       </c>
       <c r="E91" t="s">
-        <v>349</v>
+        <v>100</v>
       </c>
       <c r="F91" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
-        <v>186</v>
-      </c>
-      <c r="C92" t="s">
-        <v>187</v>
+      <c r="B92" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="D92" t="s">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="E92" t="s">
-        <v>413</v>
+        <v>164</v>
       </c>
       <c r="F92" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
-        <v>188</v>
-      </c>
-      <c r="C93" t="s">
-        <v>189</v>
+      <c r="B93" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>328</v>
       </c>
       <c r="D93" t="s">
-        <v>414</v>
+        <v>165</v>
       </c>
       <c r="E93" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="F93" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
-        <v>190</v>
-      </c>
-      <c r="C94" t="s">
-        <v>191</v>
+      <c r="B94" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="D94" t="s">
-        <v>415</v>
+        <v>166</v>
       </c>
       <c r="E94" t="s">
-        <v>298</v>
+        <v>49</v>
       </c>
       <c r="F94" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
-        <v>192</v>
-      </c>
-      <c r="C95" t="s">
-        <v>193</v>
+      <c r="B95" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>330</v>
       </c>
       <c r="D95" t="s">
-        <v>416</v>
+        <v>167</v>
       </c>
       <c r="E95" t="s">
-        <v>338</v>
+        <v>89</v>
       </c>
       <c r="F95" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
-        <v>194</v>
-      </c>
-      <c r="C96" t="s">
-        <v>195</v>
+      <c r="B96" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="D96" t="s">
-        <v>417</v>
+        <v>168</v>
       </c>
       <c r="E96" t="s">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="F96" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
-        <v>196</v>
-      </c>
-      <c r="C97" t="s">
-        <v>197</v>
+      <c r="B97" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="D97" t="s">
-        <v>418</v>
+        <v>169</v>
       </c>
       <c r="E97" t="s">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="F97" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
-        <v>198</v>
-      </c>
-      <c r="C98" t="s">
-        <v>199</v>
+      <c r="B98" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>334</v>
       </c>
       <c r="D98" t="s">
-        <v>419</v>
+        <v>170</v>
       </c>
       <c r="E98" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
       <c r="F98" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
-        <v>200</v>
-      </c>
-      <c r="C99" t="s">
-        <v>201</v>
+      <c r="B99" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="D99" t="s">
-        <v>420</v>
+        <v>171</v>
       </c>
       <c r="E99" t="s">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="F99" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
-        <v>202</v>
-      </c>
-      <c r="C100" t="s">
-        <v>203</v>
+      <c r="B100" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>336</v>
       </c>
       <c r="D100" t="s">
-        <v>421</v>
+        <v>172</v>
       </c>
       <c r="E100" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="F100" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
-        <v>204</v>
-      </c>
-      <c r="C101" t="s">
-        <v>205</v>
+      <c r="B101" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>337</v>
       </c>
       <c r="D101" t="s">
-        <v>422</v>
+        <v>173</v>
       </c>
       <c r="E101" t="s">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="F101" t="s">
-        <v>299</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3700,13 +3596,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>207</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3714,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3722,7 +3621,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3730,7 +3629,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3738,7 +3637,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -3748,34 +3647,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>213</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>215</v>
+      <c r="B2" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -3788,8 +3688,8 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>216</v>
+      <c r="B3" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3802,8 +3702,8 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>217</v>
+      <c r="B4" s="3" t="s">
+        <v>341</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -3816,8 +3716,8 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>218</v>
+      <c r="B5" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -3830,8 +3730,8 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>219</v>
+      <c r="B6" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -3844,8 +3744,8 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>220</v>
+      <c r="B7" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -3858,8 +3758,8 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>221</v>
+      <c r="B8" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -3872,8 +3772,8 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>222</v>
+      <c r="B9" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -3886,8 +3786,8 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>223</v>
+      <c r="B10" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -3900,8 +3800,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>224</v>
+      <c r="B11" s="3" t="s">
+        <v>348</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -3914,8 +3814,8 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>225</v>
+      <c r="B12" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -3928,8 +3828,8 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>226</v>
+      <c r="B13" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -3942,8 +3842,8 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>227</v>
+      <c r="B14" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -3956,8 +3856,8 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>228</v>
+      <c r="B15" s="3" t="s">
+        <v>352</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -3970,8 +3870,8 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>229</v>
+      <c r="B16" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -3984,8 +3884,8 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>230</v>
+      <c r="B17" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -3998,8 +3898,8 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>231</v>
+      <c r="B18" s="3" t="s">
+        <v>355</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -4012,8 +3912,8 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>232</v>
+      <c r="B19" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -4026,8 +3926,8 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>233</v>
+      <c r="B20" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -4040,8 +3940,8 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>234</v>
+      <c r="B21" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -4054,8 +3954,8 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>235</v>
+      <c r="B22" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -4068,8 +3968,8 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>236</v>
+      <c r="B23" s="3" t="s">
+        <v>360</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -4082,8 +3982,8 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>217</v>
+      <c r="B24" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -4096,8 +3996,8 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>237</v>
+      <c r="B25" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -4110,8 +4010,8 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>238</v>
+      <c r="B26" s="3" t="s">
+        <v>363</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -4124,8 +4024,8 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>239</v>
+      <c r="B27" s="3" t="s">
+        <v>364</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -4138,8 +4038,8 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>240</v>
+      <c r="B28" s="3" t="s">
+        <v>365</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -4152,8 +4052,8 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>241</v>
+      <c r="B29" s="3" t="s">
+        <v>366</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -4166,8 +4066,8 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>242</v>
+      <c r="B30" s="3" t="s">
+        <v>367</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -4180,8 +4080,8 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>243</v>
+      <c r="B31" s="3" t="s">
+        <v>368</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -4194,8 +4094,8 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>244</v>
+      <c r="B32" s="3" t="s">
+        <v>369</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -4208,8 +4108,8 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>245</v>
+      <c r="B33" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="C33">
         <v>4</v>
@@ -4222,8 +4122,8 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>246</v>
+      <c r="B34" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -4236,8 +4136,8 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>247</v>
+      <c r="B35" s="3" t="s">
+        <v>372</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -4250,8 +4150,8 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>248</v>
+      <c r="B36" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -4264,8 +4164,8 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>249</v>
+      <c r="B37" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -4278,8 +4178,8 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>250</v>
+      <c r="B38" s="3" t="s">
+        <v>374</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -4292,8 +4192,8 @@
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>225</v>
+      <c r="B39" s="3" t="s">
+        <v>375</v>
       </c>
       <c r="C39">
         <v>4</v>
@@ -4306,8 +4206,8 @@
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>251</v>
+      <c r="B40" s="3" t="s">
+        <v>376</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -4320,8 +4220,8 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>252</v>
+      <c r="B41" s="3" t="s">
+        <v>377</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -4334,8 +4234,8 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>253</v>
+      <c r="B42" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -4348,8 +4248,8 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>254</v>
+      <c r="B43" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -4362,8 +4262,8 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>255</v>
+      <c r="B44" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -4376,8 +4276,8 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>256</v>
+      <c r="B45" s="3" t="s">
+        <v>381</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -4390,8 +4290,8 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>257</v>
+      <c r="B46" s="3" t="s">
+        <v>382</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -4404,8 +4304,8 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>258</v>
+      <c r="B47" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -4418,8 +4318,8 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>259</v>
+      <c r="B48" s="3" t="s">
+        <v>384</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -4432,8 +4332,8 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>260</v>
+      <c r="B49" s="3" t="s">
+        <v>385</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -4446,8 +4346,8 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>261</v>
+      <c r="B50" s="3" t="s">
+        <v>386</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -4460,8 +4360,8 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
-        <v>262</v>
+      <c r="B51" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -4469,6 +4369,12 @@
       <c r="D51">
         <v>233.13</v>
       </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4480,19 +4386,20 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4500,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4511,10 +4418,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4522,10 +4429,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4533,10 +4440,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4544,10 +4451,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4555,10 +4462,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4566,10 +4473,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4577,10 +4484,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>274</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4588,10 +4495,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>275</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4599,10 +4506,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4610,10 +4517,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -4621,10 +4528,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>279</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4632,10 +4539,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>280</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4643,10 +4550,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>281</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4654,10 +4561,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -4665,10 +4572,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -4676,10 +4583,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>284</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -4687,10 +4594,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -4698,10 +4605,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>286</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4709,10 +4616,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>287</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4730,16 +4637,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>289</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>290</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>291</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11047,25 +10954,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>292</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>288</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>212</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>263</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
